--- a/data/trans_camb/IP19C09-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C09-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 6,4</t>
+          <t>-2,7; 5,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 13,3</t>
+          <t>-1,34; 12,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 5,55</t>
+          <t>-2,51; 7,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 16,37</t>
+          <t>1,22; 15,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 4,43</t>
+          <t>-1,89; 3,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 11,36</t>
+          <t>1,22; 11,53</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,16; —</t>
+          <t>-24,41; —</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,0; -1,4</t>
+          <t>-11,82; -1,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 2,83</t>
+          <t>-9,12; 3,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 6,14</t>
+          <t>-4,04; 5,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 5,57</t>
+          <t>-4,89; 5,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 1,48</t>
+          <t>-5,9; 1,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 2,63</t>
+          <t>-5,46; 2,75</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,4; 420,45</t>
+          <t>-87,7; 324,15</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,29</t>
+          <t>0,0; 7,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,53</t>
+          <t>0,0; 15,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 3,78</t>
+          <t>-6,4; 4,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 9,31</t>
+          <t>-5,61; 8,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,87</t>
+          <t>-3,48; 2,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 8,48</t>
+          <t>-2,11; 7,38</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,25</t>
+          <t>-1,26; 2,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 5,44</t>
+          <t>0,06; 6,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,48; -0,01</t>
+          <t>-7,71; 0,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 0,1</t>
+          <t>-7,48; 0,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 0,48</t>
+          <t>-3,78; 0,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 2,1</t>
+          <t>-2,93; 1,88</t>
         </is>
       </c>
     </row>
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 36,03</t>
+          <t>-100,0; 58,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 56,63</t>
+          <t>-100,0; 116,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 120,38</t>
+          <t>-100,0; 70,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-76,67; 163,21</t>
+          <t>-81,22; 146,69</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,95</t>
+          <t>0,74; 7,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,39</t>
+          <t>0,0; 6,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 0,93</t>
+          <t>-6,66; 0,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,34; -0,87</t>
+          <t>-8,73; -0,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,64</t>
+          <t>-2,56; 2,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,57</t>
+          <t>-3,79; 0,6</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 14,38</t>
+          <t>-1,86; 16,95</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 0,0</t>
+          <t>-10,14; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 0,0</t>
+          <t>-11,61; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 6,07</t>
+          <t>-7,69; 6,41</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 4,18</t>
+          <t>-4,67; 4,21</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 2,4</t>
+          <t>-5,56; 2,06</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,13</t>
+          <t>-1,03; 2,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,2</t>
+          <t>-0,38; 3,27</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 0,08</t>
+          <t>-3,66; -0,1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,32</t>
+          <t>-2,63; 1,11</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,51</t>
+          <t>-2,01; 0,59</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,76</t>
+          <t>-1,17; 1,82</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-53,04; 402,56</t>
+          <t>-63,05; 318,41</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-29,4; 542,95</t>
+          <t>-32,04; 496,01</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-85,21; 12,29</t>
+          <t>-82,43; 13,77</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-64,15; 64,64</t>
+          <t>-63,75; 52,31</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 34,28</t>
+          <t>-66,47; 44,54</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-39,31; 114,01</t>
+          <t>-39,85; 114,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C09-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C09-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 5,62</t>
+          <t>-2,7; 5,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 12,81</t>
+          <t>-1,33; 14,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 7,06</t>
+          <t>-2,51; 5,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 15,19</t>
+          <t>1,34; 16,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,9</t>
+          <t>-1,9; 4,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,53</t>
+          <t>1,07; 11,36</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-24,41; —</t>
+          <t>-50,29; —</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,82; -1,41</t>
+          <t>-12,42; -1,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 3,21</t>
+          <t>-9,81; 3,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 5,58</t>
+          <t>-5,12; 5,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 5,28</t>
+          <t>-4,21; 5,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 1,38</t>
+          <t>-6,25; 1,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 2,75</t>
+          <t>-4,92; 2,67</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,7; 324,15</t>
+          <t>-87,59; 300,72</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,23</t>
+          <t>0,0; 7,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,33</t>
+          <t>0,0; 15,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 4,6</t>
+          <t>-6,39; 4,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 8,99</t>
+          <t>-5,21; 7,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 2,69</t>
+          <t>-4,28; 2,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 7,38</t>
+          <t>-2,32; 7,11</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,7</t>
+          <t>-1,26; 2,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 6,06</t>
+          <t>-0,51; 6,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 0,02</t>
+          <t>-7,63; 0,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 0,17</t>
+          <t>-7,43; 0,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,49</t>
+          <t>-3,91; 0,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,88</t>
+          <t>-2,93; 1,84</t>
         </is>
       </c>
     </row>
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 58,91</t>
+          <t>-100,0; 48,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 116,94</t>
+          <t>-100,0; 104,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 70,9</t>
+          <t>-100,0; 95,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,22; 146,69</t>
+          <t>-79,36; 129,93</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 7,26</t>
+          <t>0,74; 7,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,1</t>
+          <t>0,0; 5,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 0,93</t>
+          <t>-6,44; 0,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,73; -0,88</t>
+          <t>-8,28; -0,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,86</t>
+          <t>-2,62; 2,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 0,6</t>
+          <t>-3,73; 0,64</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 16,95</t>
+          <t>-1,85; 15,41</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 0,0</t>
+          <t>-9,2; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 0,0</t>
+          <t>-11,4; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 6,41</t>
+          <t>-7,66; 7,11</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 4,21</t>
+          <t>-4,5; 3,82</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 2,06</t>
+          <t>-5,23; 2,4</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,0</t>
+          <t>-0,93; 2,27</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 3,27</t>
+          <t>-0,25; 3,51</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,66; -0,1</t>
+          <t>-3,72; -0,07</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,11</t>
+          <t>-2,77; 1,51</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,59</t>
+          <t>-1,84; 0,51</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,82</t>
+          <t>-1,01; 1,66</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-63,05; 318,41</t>
+          <t>-54,68; 449,82</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 496,01</t>
+          <t>-26,79; 653,84</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-82,43; 13,77</t>
+          <t>-84,79; 3,9</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-63,75; 52,31</t>
+          <t>-64,91; 70,43</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-66,47; 44,54</t>
+          <t>-63,19; 36,49</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-39,85; 114,54</t>
+          <t>-36,52; 99,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C09-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C09-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,27</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>3,3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,47</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,27</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 5,22</t>
+          <t>-2,5; 5,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 14,13</t>
+          <t>1,23; 16,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 5,59</t>
+          <t>-2,68; 6,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 16,48</t>
+          <t>-1,35; 13,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 4,28</t>
+          <t>-1,77; 4,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 11,36</t>
+          <t>1,34; 11,36</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38,01%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>584,06%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>26,07%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>247,42%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>38,01%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>584,06%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,29; —</t>
+          <t>-11,16; —</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,04</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,85</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-4,65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-2,29</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,04</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,42; -1,41</t>
+          <t>-4,34; 6,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 3,09</t>
+          <t>-4,16; 5,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 5,59</t>
+          <t>-13,0; -1,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 5,27</t>
+          <t>-10,05; 2,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 1,74</t>
+          <t>-5,92; 1,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 2,67</t>
+          <t>-4,99; 2,63</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>59,55%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>48,33%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-49,27%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>59,55%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>48,33%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,59; 300,72</t>
+          <t>-88,4; 420,45</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>1,42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>4,69</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,51</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,2</t>
+          <t>-6,38; 3,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,97</t>
+          <t>-5,34; 9,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 4,24</t>
+          <t>0,0; 7,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 7,74</t>
+          <t>0,0; 14,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 2,54</t>
+          <t>-3,36; 2,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 7,11</t>
+          <t>-2,21; 8,48</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-44,94%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-20,52%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-44,94%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-20,52%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-3,39</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-3,35</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>2,15</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,39</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-3,35</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,6</t>
+          <t>-7,48; -0,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 6,14</t>
+          <t>-7,56; 0,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 0,01</t>
+          <t>-1,27; 3,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 0,3</t>
+          <t>-0,34; 5,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,48</t>
+          <t>-3,99; 0,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,84</t>
+          <t>-2,84; 2,1</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-71,35%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-70,43%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>27,7%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>342,24%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-71,35%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-70,43%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 36,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 56,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 48,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 104,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 95,4</t>
+          <t>-100,0; 120,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,36; 129,93</t>
+          <t>-76,67; 163,21</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-2,09</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-3,01</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>2,65</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1,17</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-2,09</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-3,01</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 7,24</t>
+          <t>-7,65; 0,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,82</t>
+          <t>-8,34; -0,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 0,94</t>
+          <t>0,73; 6,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,28; -0,87</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 2,66</t>
+          <t>-2,35; 2,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,64</t>
+          <t>-3,87; 0,57</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-69,31%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-69,31%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-3,79</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-1,38</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>3,66</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-1,83</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-3,79</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-1,38</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 15,41</t>
+          <t>-11,49; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>-7,57; 6,07</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>-2,71; 14,38</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>-9,2; 0,0</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>-11,4; 0,0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>-7,66; 7,11</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 3,82</t>
+          <t>-4,59; 4,18</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 2,4</t>
+          <t>-5,45; 2,4</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-36,46%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>199,94%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-36,46%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-1,81</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,49</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1,3</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-1,81</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,27</t>
+          <t>-3,8; 0,08</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 3,51</t>
+          <t>-2,71; 1,32</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,72; -0,07</t>
+          <t>-0,82; 2,13</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,51</t>
+          <t>-0,37; 3,2</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,51</t>
+          <t>-1,93; 0,51</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,66</t>
+          <t>-1,05; 1,76</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-55,7%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-21,31%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>39,62%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>105,61%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-55,7%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-21,31%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-54,68; 449,82</t>
+          <t>-85,21; 12,29</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 653,84</t>
+          <t>-64,15; 64,64</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-84,79; 3,9</t>
+          <t>-53,04; 402,56</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-64,91; 70,43</t>
+          <t>-29,4; 542,95</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-63,19; 36,49</t>
+          <t>-65,77; 34,28</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-36,52; 99,22</t>
+          <t>-39,31; 114,01</t>
         </is>
       </c>
     </row>
